--- a/samples/shop-analytics/shopify-quarter.xlsx
+++ b/samples/shop-analytics/shopify-quarter.xlsx
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Before any work: the contracts, the export against Shopify's own record, the plan's proof</t>
+          <t>Before any work: the contracts, the export against its control file, the plan's proof</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Какой статус заказа считается продажей в отчётном периоде?</t>
+          <t>Which order status counts as a sale in the period?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Как считать отменённые заказы?</t>
+          <t>How are cancelled orders counted?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Как распознаются и куда деваются тестовые и внутренние заказы?</t>
+          <t>How are test and internal orders recognised, and where do they go?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Что такое одна строка популяции: заказ или строка заказа?</t>
+          <t>Is one row of the population an order or an order line?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Чьи продажи входят в отчёт: собственные, продавцов площадки или обе группы?</t>
+          <t>Whose sales are in the report: the shop's own, marketplace sellers', or both?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>На какой базе считается ставка возвратов?</t>
+          <t>What is the refund rate taken over?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Как считается частичный возврат?</t>
+          <t>How is a partial refund counted?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>К какому периоду относится возврат: к периоду заказа или к периоду возврата?</t>
+          <t>Which period does a refund belong to: the order's or the refund's?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Что входит в сумму возврата: только товар, или и доставка, и комиссии?</t>
+          <t>What does a refund amount include: the goods only, or shipping and fees too?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Какая дата определяет принадлежность заказа периоду?</t>
+          <t>Which date puts an order in a period?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Границы периода включительные с обеих сторон или конец исключён?</t>
+          <t>Are the period's bounds inclusive at both ends, or is the end excluded?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>В каком часовом поясе читается дата события?</t>
+          <t>In which time zone is an event's date read?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Как читается строка заказа, у которой несколько версий в выгрузке?</t>
+          <t>How is an order line read when the export holds several versions of it?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Что такое выручка в заголовке: до или после возвратов?</t>
+          <t>Is the headline revenue before or after refunds?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Суммы в выручке с НДС или без?</t>
+          <t>Are revenue amounts with VAT or without?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Сумма заказа берётся до или после скидок и промокодов?</t>
+          <t>Is an order's amount taken before or after discounts and codes?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Плата за доставку входит в выручку?</t>
+          <t>Is the shipping fee revenue?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>В какой валюте и по какому курсу суммируются заказы в разных валютах?</t>
+          <t>In which currency, and at which rate, are orders in different currencies added up?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Где округляются суммы: по строке или в итоге?</t>
+          <t>Where are amounts rounded: per line or in the total?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Что такое один клиент?</t>
+          <t>What is one customer?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Как считать заказы без аккаунта (гостевые)?</t>
+          <t>How are orders without an account (guest checkouts) counted?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Кто такой новый клиент периода?</t>
+          <t>Who is a new customer of the period?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Кто такой платящий клиент в знаменателе ставок?</t>
+          <t>Who is a paying customer in the denominator of a rate?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Что такое количество в строке: штуки, упаковки или вес?</t>
+          <t>What is the quantity on a line: pieces, packs or weight?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Как считается набор (бандл) из нескольких товаров?</t>
+          <t>How is a bundle of several products counted?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Что означает отрицательное количество или отрицательная сумма в строке?</t>
+          <t>What does a negative quantity or amount on a line mean?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Как считать строки с нулевой суммой?</t>
+          <t>How are rows with a zero amount counted?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Что такое канал заказа?</t>
+          <t>What is an order's channel?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Как заказ относится к промокампании?</t>
+          <t>How is an order attributed to a promotion?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Куда идут заказы с пустым или неизвестным каналом?</t>
+          <t>Where do orders with an empty or unknown channel go?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Что делать с повторяющимся идентификатором заказа?</t>
+          <t>What is done with a repeated order id?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Как поступать, если выгрузка не покрывает весь отчётный период?</t>
+          <t>What if the export does not cover the whole period?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Как считать строки с пустой суммой?</t>
+          <t>How are rows with an empty amount counted?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Что делать с колонками свободного текста (комментарии, адреса, заметки)?</t>
+          <t>What is done with free-text columns: comments, addresses, notes?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3193,7 +3193,11 @@
           <t>product_sales_basis</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>What are a product's sales?</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>after_discounts_before_refunds</t>
@@ -3211,7 +3215,11 @@
           <t>discount_share_basis</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>What is the discount share taken over?</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>discounts_over_gross_sales</t>
@@ -3229,7 +3237,11 @@
           <t>repeat_customer_basis</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Who is a returning customer?</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>repeat_within_period</t>
@@ -3247,7 +3259,11 @@
           <t>aov_basis</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>What is the average order value?</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>net_sales_per_order</t>
@@ -3294,7 +3310,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Shopify's record</t>
+          <t>The control file (written by the generator)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
